--- a/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD008CB8-6655-4D93-880C-5DAFF402F70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E8AECB7-2994-4381-AB80-9CB36BF79B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{96A454DA-8C01-40AE-A03A-E84EB6B7709A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{06D90E90-058C-451A-9A99-AE00FA9E05B8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E902BE7-533C-4511-9E91-508D7237A029}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A1365B-3F42-4A47-B1EF-BD6075E64AFB}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E8AECB7-2994-4381-AB80-9CB36BF79B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9B56325-495F-4D52-9000-4D6C5E1C4CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{06D90E90-058C-451A-9A99-AE00FA9E05B8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{25CFD449-585C-4608-B33F-EB31ADD6594F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A1365B-3F42-4A47-B1EF-BD6075E64AFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA3B56E-A975-4A9C-A225-8E5C52D59F88}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_CAN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9B56325-495F-4D52-9000-4D6C5E1C4CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9C357D4-9CCF-4BD3-993F-646966813D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{25CFD449-585C-4608-B33F-EB31ADD6594F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2735E7DC-B539-482C-A0E9-1C7936C77F50}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -4462,7 +4462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA3B56E-A975-4A9C-A225-8E5C52D59F88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB41545D-B61A-4340-A693-53AE47D993AE}">
   <dimension ref="B3:L566"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
